--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_FashionGuide.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_FashionGuide.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_FashionGuide" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -95,7 +95,7 @@
     <t>icon</t>
   </si>
   <si>
-    <t>皇家</t>
+    <t>焚天之烬灭</t>
   </si>
   <si>
     <t>20301051#20401051#20601051#20801051#20701051#20901051</t>
@@ -104,7 +104,7 @@
     <t>hjjw</t>
   </si>
   <si>
-    <t>冰霜</t>
+    <t>霜魄之凝殇</t>
   </si>
   <si>
     <t>21010301#21040301#21060301#21070301#21080301#21090301</t>
@@ -113,7 +113,7 @@
     <t>bszyd</t>
   </si>
   <si>
-    <t>次元</t>
+    <t>星墟之耀芒</t>
   </si>
   <si>
     <t>21010201#21040201#21060201#21070201#21080201#21090201</t>
@@ -122,16 +122,13 @@
     <t>cyzxx</t>
   </si>
   <si>
-    <t>时空</t>
+    <t>星穹撕裂者</t>
   </si>
   <si>
     <t>21010101#21040101#21060101#21070101#21080101#21090101</t>
   </si>
   <si>
     <t>skyqz</t>
-  </si>
-  <si>
-    <t>20102051#20202052#20402051#20602051#20802051#20702051#20902051</t>
   </si>
   <si>
     <t>21010302#21020302#21040302#21060302#21070302#21080302#21090302</t>
@@ -165,18 +162,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -643,145 +635,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -835,24 +824,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1046,25 +1018,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1325,7 +1297,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.875" customWidth="1"/>
@@ -1519,7 +1491,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>5</v>
       </c>
@@ -1535,8 +1507,8 @@
       <c r="E9">
         <v>7</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>34</v>
+      <c r="F9" t="s">
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -1559,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" t="s">
         <v>27</v>
@@ -1582,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
         <v>30</v>
@@ -1605,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
         <v>33</v>
@@ -1628,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -1651,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
         <v>27</v>
@@ -1674,7 +1646,7 @@
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
         <v>30</v>
@@ -1697,21 +1669,381 @@
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
+        <v>6</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+      <c r="D30">
+        <v>7</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>6</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F9">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>AND(SUMPRODUCT(IFERROR(1*(($F$9&amp;"x")=(F9&amp;"x")),0))&gt;1,NOT(ISBLANK(F9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_FashionGuide.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_FashionGuide.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_FashionGuide" sheetId="1" r:id="rId1"/>
